--- a/procedures/E5_Tableau-de-synthese.xlsx
+++ b/procedures/E5_Tableau-de-synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduservices.sharepoint.com/teams/BTSSIO20252026/Documents partages/General/Dossiers professionnels - Épreuves orales/E5 - Support et mise à disposition de services informatiques/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{697E435F-A779-4900-8DC3-6D7AEC31E0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FBD0AB-2F54-45F1-B4B6-A4B0CF7AEFDB}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{697E435F-A779-4900-8DC3-6D7AEC31E0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E6CD29B-D235-4273-9C10-59AF301507DF}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1560,16 +1560,16 @@
       <c r="B13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="20" t="s">
         <v>27</v>
       </c>
       <c r="I13"/>
@@ -1615,20 +1615,20 @@
       <c r="B14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23" t="s">
+      <c r="F14" s="19"/>
+      <c r="G14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="20" t="s">
         <v>27</v>
       </c>
       <c r="I14"/>
